--- a/database/raw/math_models/60 Hz.xlsx
+++ b/database/raw/math_models/60 Hz.xlsx
@@ -5,17 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="60 HZ Prueba 1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="60 HZ Pueba 2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="60 HZ Prueba 2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="60 HZ Prueba 3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'60 HZ Prueba 1'!$A$1:$D$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'60 HZ Prueba 2'!$A$1:$D$11</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'60 HZ Prueba 3'!$A$1:$D$10</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'60 HZ Pueba 2'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -138,20 +138,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -163,7 +167,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -479,105 +483,105 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="3" t="n">
         <v>13.31</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="3" t="n">
         <v>13.93</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>10.1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>10.78</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>13.9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>9.83</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>10.47</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>12.04</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>8.51</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>9.09</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>11.56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <v>8.43</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>9.14</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>14.14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>7.94</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>8.62</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>11.91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="3" t="n">
         <v>8.36</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="3" t="n">
         <v>9.04</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>13.85</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="5"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -616,94 +620,94 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="3" t="n">
         <v>13.01</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="3" t="n">
         <v>14.04</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>10.15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>10.85</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="3" t="n">
         <v>11.88</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>11.51</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>8.86</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>9.88</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>12.49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>8.06</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>9.11</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>11.86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <v>7.81</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>8.97</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>11.82</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>7.38</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>8.46</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>14.23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D8" s="3"/>
+      <c r="D8" s="4"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D9" s="5"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -742,100 +746,100 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>1800</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="3" t="n">
         <v>13.22</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="3" t="n">
         <v>14.28</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>11.73</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>1500</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>10.87</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="3" t="n">
         <v>11.91</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>12.09</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>9.02</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>10.06</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>15.7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>6.05</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>6.85</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>11.73</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>7.6</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>8.71</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>11.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>7.47</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>8.56</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>12.83</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="3" t="n">
         <v>12.31</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="3" t="n">
         <v>13.44</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>12.43</v>
       </c>
     </row>
